--- a/input/mapping/061. OCB_GOLD_TCKH_V_TB_NIM_1_HOP.xlsx
+++ b/input/mapping/061. OCB_GOLD_TCKH_V_TB_NIM_1_HOP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1738" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E45983CE-0B85-40A3-9E71-5368F7ADDD63}"/>
+  <xr:revisionPtr revIDLastSave="1741" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6BFFCF2-4D20-445A-A4F6-26C2FEF9D606}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -881,11 +881,57 @@
     LEFT JOIN V_BRANCH_LIST D
         ON  Z3.BRANCH_CODE = D.BRANCH_CODE
 )
-SELECT * FROM BLOCK1
+-- 3.1: liệt kê tường minh 57 cột thay SELECT *
+SELECT
+    SECTOR, SECTOR_NAME, PROMOTION_ID, PROMOTION_NAME, PURPOSE_NO, PURPOSE_NAME,
+    DATA_DATE, CDR_DT_ID, TERM, PRODUCT_CODE, PRODUCT_NAME,
+    SUBPRODUCT_CODE, SUBPRODUCT_NAME,
+    INDUSTRY, INDUSTRY_LEV1, INDUSTRY_LEV1_DSC,
+    INDUSTRY_LEV2, INDUSTRY_LEV2_DSC, INDUSTRY_LEV3, INDUSTRY_LEV3_DSC,
+    INTEREST_BASIS, INTEREST_SPREAD, INTEREST_RATE,
+    FTP_RATE, FTP_PD_RATE, INT_RATE_TYPE, BASE_INTEREST_RATE,
+    CONTRACT_NO, AR_ID, PD_PR_AMT, GL, TERM_D, END_DATE, START_DATE, CURRENCY,
+    IN_AMT, IN_AMT_EQ, AMT, AMT_EQ, PD_AMOUNT_EQ, LD_AMOUNT_EQ,
+    COLLATERAL_TYPE, CIF, FULL_NM,
+    PRN_BRANCH_NAME, PRN_BRANCH_CODE, BRANCH_NAME, BRANCH_CODE,
+    OFFICER_ID_CIF, OFFICER_ID_CIF_NAME, OFFICER_ID_ACC, OFFICER_NAME_ACC,
+    CUSTGROUP, CUST_GROUP_NAME, LOAN_CLASS,
+    FTP_INTEREST_RATE_NIM_ON, LIFE_CYCLE_STATUS
+FROM BLOCK1
 UNION ALL
-SELECT * FROM BLOCK2
+SELECT
+    SECTOR, SECTOR_NAME, PROMOTION_ID, PROMOTION_NAME, PURPOSE_NO, PURPOSE_NAME,
+    DATA_DATE, CDR_DT_ID, TERM, PRODUCT_CODE, PRODUCT_NAME,
+    SUBPRODUCT_CODE, SUBPRODUCT_NAME,
+    INDUSTRY, INDUSTRY_LEV1, INDUSTRY_LEV1_DSC,
+    INDUSTRY_LEV2, INDUSTRY_LEV2_DSC, INDUSTRY_LEV3, INDUSTRY_LEV3_DSC,
+    INTEREST_BASIS, INTEREST_SPREAD, INTEREST_RATE,
+    FTP_RATE, FTP_PD_RATE, INT_RATE_TYPE, BASE_INTEREST_RATE,
+    CONTRACT_NO, AR_ID, PD_PR_AMT, GL, TERM_D, END_DATE, START_DATE, CURRENCY,
+    IN_AMT, IN_AMT_EQ, AMT, AMT_EQ, PD_AMOUNT_EQ, LD_AMOUNT_EQ,
+    COLLATERAL_TYPE, CIF, FULL_NM,
+    PRN_BRANCH_NAME, PRN_BRANCH_CODE, BRANCH_NAME, BRANCH_CODE,
+    OFFICER_ID_CIF, OFFICER_ID_CIF_NAME, OFFICER_ID_ACC, OFFICER_NAME_ACC,
+    CUSTGROUP, CUST_GROUP_NAME, LOAN_CLASS,
+    FTP_INTEREST_RATE_NIM_ON, LIFE_CYCLE_STATUS
+FROM BLOCK2
 UNION ALL
-SELECT * FROM BLOCK3
+SELECT
+    SECTOR, SECTOR_NAME, PROMOTION_ID, PROMOTION_NAME, PURPOSE_NO, PURPOSE_NAME,
+    DATA_DATE, CDR_DT_ID, TERM, PRODUCT_CODE, PRODUCT_NAME,
+    SUBPRODUCT_CODE, SUBPRODUCT_NAME,
+    INDUSTRY, INDUSTRY_LEV1, INDUSTRY_LEV1_DSC,
+    INDUSTRY_LEV2, INDUSTRY_LEV2_DSC, INDUSTRY_LEV3, INDUSTRY_LEV3_DSC,
+    INTEREST_BASIS, INTEREST_SPREAD, INTEREST_RATE,
+    FTP_RATE, FTP_PD_RATE, INT_RATE_TYPE, BASE_INTEREST_RATE,
+    CONTRACT_NO, AR_ID, PD_PR_AMT, GL, TERM_D, END_DATE, START_DATE, CURRENCY,
+    IN_AMT, IN_AMT_EQ, AMT, AMT_EQ, PD_AMOUNT_EQ, LD_AMOUNT_EQ,
+    COLLATERAL_TYPE, CIF, FULL_NM,
+    PRN_BRANCH_NAME, PRN_BRANCH_CODE, BRANCH_NAME, BRANCH_CODE,
+    OFFICER_ID_CIF, OFFICER_ID_CIF_NAME, OFFICER_ID_ACC, OFFICER_NAME_ACC,
+    CUSTGROUP, CUST_GROUP_NAME, LOAN_CLASS,
+    FTP_INTEREST_RATE_NIM_ON, LIFE_CYCLE_STATUS
+FROM BLOCK3
 ;</t>
   </si>
   <si>
@@ -4388,6 +4434,207 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="8" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="8" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="8" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="8" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="13" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="13" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="13" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4397,90 +4644,6 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="13" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="13" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="13" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4498,123 +4661,6 @@
     </xf>
     <xf numFmtId="0" fontId="36" fillId="8" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="8" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="8" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="8" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="8" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4824,7 +4870,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -5193,26 +5239,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="30" customHeight="1">
-      <c r="A1" s="196" t="s">
+      <c r="A1" s="263" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="197"/>
-      <c r="C1" s="197"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="197"/>
-      <c r="F1" s="197"/>
-      <c r="G1" s="197"/>
-      <c r="H1" s="197"/>
-      <c r="I1" s="197"/>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="198"/>
+      <c r="B1" s="264"/>
+      <c r="C1" s="264"/>
+      <c r="D1" s="264"/>
+      <c r="E1" s="264"/>
+      <c r="F1" s="264"/>
+      <c r="G1" s="264"/>
+      <c r="H1" s="264"/>
+      <c r="I1" s="264"/>
+      <c r="J1" s="264"/>
+      <c r="K1" s="264"/>
+      <c r="L1" s="264"/>
+      <c r="M1" s="264"/>
+      <c r="N1" s="264"/>
+      <c r="O1" s="264"/>
+      <c r="P1" s="264"/>
+      <c r="Q1" s="264"/>
+      <c r="R1" s="265"/>
       <c r="S1" s="40"/>
       <c r="T1" s="40"/>
       <c r="U1" s="40"/>
@@ -5245,91 +5291,91 @@
       <c r="AV1" s="40"/>
     </row>
     <row r="2" spans="1:48">
-      <c r="A2" s="254" t="s">
+      <c r="A2" s="214" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="255"/>
-      <c r="C2" s="256"/>
-      <c r="D2" s="199" t="s">
+      <c r="B2" s="215"/>
+      <c r="C2" s="216"/>
+      <c r="D2" s="233" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="238" t="s">
+      <c r="E2" s="236" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="239"/>
-      <c r="G2" s="235" t="s">
+      <c r="F2" s="237"/>
+      <c r="G2" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="223" t="s">
+      <c r="H2" s="208" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="224"/>
-      <c r="J2" s="235" t="s">
+      <c r="I2" s="209"/>
+      <c r="J2" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="227" t="s">
+      <c r="K2" s="266" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="228"/>
-      <c r="M2" s="235" t="s">
+      <c r="L2" s="267"/>
+      <c r="M2" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="223" t="s">
+      <c r="N2" s="208" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="224"/>
-      <c r="P2" s="235" t="s">
+      <c r="O2" s="209"/>
+      <c r="P2" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="Q2" s="263" t="s">
+      <c r="Q2" s="196" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="264"/>
+      <c r="R2" s="197"/>
     </row>
     <row r="3" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A3" s="257"/>
-      <c r="B3" s="258"/>
-      <c r="C3" s="259"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="241"/>
-      <c r="G3" s="236"/>
-      <c r="H3" s="233"/>
-      <c r="I3" s="234"/>
-      <c r="J3" s="236"/>
-      <c r="K3" s="229"/>
-      <c r="L3" s="230"/>
-      <c r="M3" s="236"/>
-      <c r="N3" s="233"/>
-      <c r="O3" s="234"/>
-      <c r="P3" s="236"/>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="266"/>
+      <c r="A3" s="217"/>
+      <c r="B3" s="218"/>
+      <c r="C3" s="219"/>
+      <c r="D3" s="234"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="239"/>
+      <c r="G3" s="203"/>
+      <c r="H3" s="210"/>
+      <c r="I3" s="211"/>
+      <c r="J3" s="203"/>
+      <c r="K3" s="268"/>
+      <c r="L3" s="269"/>
+      <c r="M3" s="203"/>
+      <c r="N3" s="210"/>
+      <c r="O3" s="211"/>
+      <c r="P3" s="203"/>
+      <c r="Q3" s="198"/>
+      <c r="R3" s="199"/>
     </row>
     <row r="4" spans="1:48">
-      <c r="A4" s="257"/>
-      <c r="B4" s="258"/>
-      <c r="C4" s="259"/>
-      <c r="D4" s="201"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="243"/>
-      <c r="G4" s="237"/>
-      <c r="H4" s="225"/>
-      <c r="I4" s="226"/>
-      <c r="J4" s="237"/>
-      <c r="K4" s="231"/>
-      <c r="L4" s="232"/>
-      <c r="M4" s="237"/>
-      <c r="N4" s="225"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="237"/>
-      <c r="Q4" s="267"/>
-      <c r="R4" s="268"/>
+      <c r="A4" s="217"/>
+      <c r="B4" s="218"/>
+      <c r="C4" s="219"/>
+      <c r="D4" s="235"/>
+      <c r="E4" s="240"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="204"/>
+      <c r="H4" s="212"/>
+      <c r="I4" s="213"/>
+      <c r="J4" s="204"/>
+      <c r="K4" s="270"/>
+      <c r="L4" s="271"/>
+      <c r="M4" s="204"/>
+      <c r="N4" s="212"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="204"/>
+      <c r="Q4" s="200"/>
+      <c r="R4" s="201"/>
     </row>
     <row r="5" spans="1:48" ht="37.5" customHeight="1">
-      <c r="A5" s="257"/>
-      <c r="B5" s="258"/>
-      <c r="C5" s="259"/>
+      <c r="A5" s="217"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="219"/>
       <c r="G5" s="138"/>
       <c r="J5" s="137"/>
       <c r="K5" s="137"/>
@@ -5339,23 +5385,23 @@
       <c r="O5" s="137"/>
     </row>
     <row r="6" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A6" s="257"/>
-      <c r="B6" s="258"/>
-      <c r="C6" s="259"/>
-      <c r="D6" s="199" t="s">
+      <c r="A6" s="217"/>
+      <c r="B6" s="218"/>
+      <c r="C6" s="219"/>
+      <c r="D6" s="233" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="244" t="s">
+      <c r="E6" s="242" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="245"/>
+      <c r="F6" s="243"/>
       <c r="G6" s="187" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="223" t="s">
+      <c r="H6" s="208" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="224"/>
+      <c r="I6" s="209"/>
       <c r="J6" s="137"/>
       <c r="K6" s="137"/>
       <c r="L6" s="173"/>
@@ -5364,15 +5410,15 @@
       <c r="O6" s="137"/>
     </row>
     <row r="7" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A7" s="257"/>
-      <c r="B7" s="258"/>
-      <c r="C7" s="259"/>
-      <c r="D7" s="201"/>
-      <c r="E7" s="246"/>
-      <c r="F7" s="247"/>
+      <c r="A7" s="217"/>
+      <c r="B7" s="218"/>
+      <c r="C7" s="219"/>
+      <c r="D7" s="235"/>
+      <c r="E7" s="244"/>
+      <c r="F7" s="245"/>
       <c r="G7" s="188"/>
-      <c r="H7" s="225"/>
-      <c r="I7" s="226"/>
+      <c r="H7" s="212"/>
+      <c r="I7" s="213"/>
       <c r="J7" s="137"/>
       <c r="K7" s="137"/>
       <c r="L7" s="173"/>
@@ -5381,9 +5427,9 @@
       <c r="O7" s="137"/>
     </row>
     <row r="8" spans="1:48" ht="28.5" customHeight="1">
-      <c r="A8" s="257"/>
-      <c r="B8" s="258"/>
-      <c r="C8" s="259"/>
+      <c r="A8" s="217"/>
+      <c r="B8" s="218"/>
+      <c r="C8" s="219"/>
       <c r="J8" s="137"/>
       <c r="K8" s="137"/>
       <c r="L8" s="137"/>
@@ -5392,147 +5438,147 @@
       <c r="O8" s="137"/>
     </row>
     <row r="9" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A9" s="257"/>
-      <c r="B9" s="258"/>
-      <c r="C9" s="259"/>
-      <c r="D9" s="199" t="s">
+      <c r="A9" s="217"/>
+      <c r="B9" s="218"/>
+      <c r="C9" s="219"/>
+      <c r="D9" s="233" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="244" t="s">
+      <c r="E9" s="242" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="245"/>
-      <c r="G9" s="202" t="s">
+      <c r="F9" s="243"/>
+      <c r="G9" s="260" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="205" t="s">
+      <c r="H9" s="227" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="206"/>
-      <c r="J9" s="202" t="s">
+      <c r="I9" s="228"/>
+      <c r="J9" s="260" t="s">
         <v>2</v>
       </c>
-      <c r="K9" s="205" t="s">
+      <c r="K9" s="227" t="s">
         <v>13</v>
       </c>
-      <c r="L9" s="206"/>
-      <c r="M9" s="202" t="s">
+      <c r="L9" s="228"/>
+      <c r="M9" s="260" t="s">
         <v>2</v>
       </c>
-      <c r="N9" s="211" t="s">
+      <c r="N9" s="248" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="212"/>
+      <c r="O9" s="249"/>
     </row>
     <row r="10" spans="1:48">
-      <c r="A10" s="257"/>
-      <c r="B10" s="258"/>
-      <c r="C10" s="259"/>
-      <c r="D10" s="200"/>
-      <c r="E10" s="248"/>
-      <c r="F10" s="249"/>
-      <c r="G10" s="203"/>
-      <c r="H10" s="207"/>
-      <c r="I10" s="208"/>
-      <c r="J10" s="203"/>
-      <c r="K10" s="207"/>
-      <c r="L10" s="208"/>
-      <c r="M10" s="203"/>
-      <c r="N10" s="213"/>
-      <c r="O10" s="214"/>
+      <c r="A10" s="217"/>
+      <c r="B10" s="218"/>
+      <c r="C10" s="219"/>
+      <c r="D10" s="234"/>
+      <c r="E10" s="246"/>
+      <c r="F10" s="247"/>
+      <c r="G10" s="261"/>
+      <c r="H10" s="229"/>
+      <c r="I10" s="230"/>
+      <c r="J10" s="261"/>
+      <c r="K10" s="229"/>
+      <c r="L10" s="230"/>
+      <c r="M10" s="261"/>
+      <c r="N10" s="250"/>
+      <c r="O10" s="251"/>
     </row>
     <row r="11" spans="1:48">
-      <c r="A11" s="257"/>
-      <c r="B11" s="258"/>
-      <c r="C11" s="259"/>
-      <c r="D11" s="200"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="249"/>
-      <c r="G11" s="203"/>
-      <c r="H11" s="207"/>
-      <c r="I11" s="208"/>
-      <c r="J11" s="203"/>
-      <c r="K11" s="207"/>
-      <c r="L11" s="208"/>
-      <c r="M11" s="204"/>
-      <c r="N11" s="215"/>
-      <c r="O11" s="216"/>
+      <c r="A11" s="217"/>
+      <c r="B11" s="218"/>
+      <c r="C11" s="219"/>
+      <c r="D11" s="234"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="247"/>
+      <c r="G11" s="261"/>
+      <c r="H11" s="229"/>
+      <c r="I11" s="230"/>
+      <c r="J11" s="261"/>
+      <c r="K11" s="229"/>
+      <c r="L11" s="230"/>
+      <c r="M11" s="262"/>
+      <c r="N11" s="252"/>
+      <c r="O11" s="253"/>
     </row>
     <row r="12" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A12" s="257"/>
-      <c r="B12" s="258"/>
-      <c r="C12" s="259"/>
-      <c r="D12" s="200"/>
-      <c r="E12" s="248"/>
-      <c r="F12" s="249"/>
-      <c r="G12" s="203"/>
-      <c r="H12" s="207"/>
-      <c r="I12" s="208"/>
-      <c r="J12" s="203"/>
-      <c r="K12" s="207"/>
-      <c r="L12" s="208"/>
+      <c r="A12" s="217"/>
+      <c r="B12" s="218"/>
+      <c r="C12" s="219"/>
+      <c r="D12" s="234"/>
+      <c r="E12" s="246"/>
+      <c r="F12" s="247"/>
+      <c r="G12" s="261"/>
+      <c r="H12" s="229"/>
+      <c r="I12" s="230"/>
+      <c r="J12" s="261"/>
+      <c r="K12" s="229"/>
+      <c r="L12" s="230"/>
       <c r="N12" s="140"/>
       <c r="O12" s="140"/>
     </row>
     <row r="13" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A13" s="257"/>
-      <c r="B13" s="258"/>
-      <c r="C13" s="259"/>
-      <c r="D13" s="200"/>
-      <c r="E13" s="248"/>
-      <c r="F13" s="249"/>
-      <c r="G13" s="203"/>
-      <c r="H13" s="207"/>
-      <c r="I13" s="208"/>
-      <c r="J13" s="203"/>
-      <c r="K13" s="207"/>
-      <c r="L13" s="208"/>
-      <c r="M13" s="202" t="s">
+      <c r="A13" s="217"/>
+      <c r="B13" s="218"/>
+      <c r="C13" s="219"/>
+      <c r="D13" s="234"/>
+      <c r="E13" s="246"/>
+      <c r="F13" s="247"/>
+      <c r="G13" s="261"/>
+      <c r="H13" s="229"/>
+      <c r="I13" s="230"/>
+      <c r="J13" s="261"/>
+      <c r="K13" s="229"/>
+      <c r="L13" s="230"/>
+      <c r="M13" s="260" t="s">
         <v>2</v>
       </c>
-      <c r="N13" s="217" t="s">
+      <c r="N13" s="254" t="s">
         <v>15</v>
       </c>
-      <c r="O13" s="218"/>
+      <c r="O13" s="255"/>
     </row>
     <row r="14" spans="1:48">
-      <c r="A14" s="257"/>
-      <c r="B14" s="258"/>
-      <c r="C14" s="259"/>
-      <c r="D14" s="200"/>
-      <c r="E14" s="248"/>
-      <c r="F14" s="249"/>
-      <c r="G14" s="203"/>
-      <c r="H14" s="207"/>
-      <c r="I14" s="208"/>
-      <c r="J14" s="203"/>
-      <c r="K14" s="207"/>
-      <c r="L14" s="208"/>
-      <c r="M14" s="203"/>
-      <c r="N14" s="219"/>
-      <c r="O14" s="220"/>
+      <c r="A14" s="217"/>
+      <c r="B14" s="218"/>
+      <c r="C14" s="219"/>
+      <c r="D14" s="234"/>
+      <c r="E14" s="246"/>
+      <c r="F14" s="247"/>
+      <c r="G14" s="261"/>
+      <c r="H14" s="229"/>
+      <c r="I14" s="230"/>
+      <c r="J14" s="261"/>
+      <c r="K14" s="229"/>
+      <c r="L14" s="230"/>
+      <c r="M14" s="261"/>
+      <c r="N14" s="256"/>
+      <c r="O14" s="257"/>
     </row>
     <row r="15" spans="1:48">
-      <c r="A15" s="257"/>
-      <c r="B15" s="258"/>
-      <c r="C15" s="259"/>
-      <c r="D15" s="201"/>
-      <c r="E15" s="246"/>
-      <c r="F15" s="247"/>
-      <c r="G15" s="204"/>
-      <c r="H15" s="209"/>
-      <c r="I15" s="210"/>
-      <c r="J15" s="204"/>
-      <c r="K15" s="209"/>
-      <c r="L15" s="210"/>
-      <c r="M15" s="204"/>
-      <c r="N15" s="221"/>
-      <c r="O15" s="222"/>
+      <c r="A15" s="217"/>
+      <c r="B15" s="218"/>
+      <c r="C15" s="219"/>
+      <c r="D15" s="235"/>
+      <c r="E15" s="244"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="262"/>
+      <c r="H15" s="231"/>
+      <c r="I15" s="232"/>
+      <c r="J15" s="262"/>
+      <c r="K15" s="231"/>
+      <c r="L15" s="232"/>
+      <c r="M15" s="262"/>
+      <c r="N15" s="258"/>
+      <c r="O15" s="259"/>
     </row>
     <row r="16" spans="1:48">
-      <c r="A16" s="257"/>
-      <c r="B16" s="258"/>
-      <c r="C16" s="259"/>
+      <c r="A16" s="217"/>
+      <c r="B16" s="218"/>
+      <c r="C16" s="219"/>
       <c r="J16" s="137"/>
       <c r="K16" s="137"/>
       <c r="L16" s="137"/>
@@ -5540,16 +5586,16 @@
       <c r="N16" s="137"/>
     </row>
     <row r="17" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A17" s="257"/>
-      <c r="B17" s="258"/>
-      <c r="C17" s="259"/>
-      <c r="D17" s="199" t="s">
+      <c r="A17" s="217"/>
+      <c r="B17" s="218"/>
+      <c r="C17" s="219"/>
+      <c r="D17" s="233" t="s">
         <v>2</v>
       </c>
-      <c r="E17" s="250" t="s">
+      <c r="E17" s="223" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="251"/>
+      <c r="F17" s="224"/>
       <c r="J17" s="137"/>
       <c r="K17" s="137"/>
       <c r="L17" s="137"/>
@@ -5558,12 +5604,12 @@
       <c r="O17" s="137"/>
     </row>
     <row r="18" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A18" s="257"/>
-      <c r="B18" s="258"/>
-      <c r="C18" s="259"/>
-      <c r="D18" s="201"/>
-      <c r="E18" s="252"/>
-      <c r="F18" s="253"/>
+      <c r="A18" s="217"/>
+      <c r="B18" s="218"/>
+      <c r="C18" s="219"/>
+      <c r="D18" s="235"/>
+      <c r="E18" s="225"/>
+      <c r="F18" s="226"/>
       <c r="J18" s="137"/>
       <c r="K18" s="137"/>
       <c r="L18" s="137"/>
@@ -5572,9 +5618,9 @@
       <c r="O18" s="137"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="257"/>
-      <c r="B19" s="258"/>
-      <c r="C19" s="259"/>
+      <c r="A19" s="217"/>
+      <c r="B19" s="218"/>
+      <c r="C19" s="219"/>
       <c r="J19" s="137"/>
       <c r="K19" s="137"/>
       <c r="L19" s="137"/>
@@ -5583,16 +5629,16 @@
       <c r="O19" s="137"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="257"/>
-      <c r="B20" s="258"/>
-      <c r="C20" s="259"/>
-      <c r="D20" s="199" t="s">
+      <c r="A20" s="217"/>
+      <c r="B20" s="218"/>
+      <c r="C20" s="219"/>
+      <c r="D20" s="233" t="s">
         <v>2</v>
       </c>
-      <c r="E20" s="250" t="s">
+      <c r="E20" s="223" t="s">
         <v>17</v>
       </c>
-      <c r="F20" s="251"/>
+      <c r="F20" s="224"/>
       <c r="J20" s="137"/>
       <c r="K20" s="137"/>
       <c r="L20" s="137"/>
@@ -5601,116 +5647,116 @@
       <c r="O20" s="137"/>
     </row>
     <row r="21" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A21" s="257"/>
-      <c r="B21" s="258"/>
-      <c r="C21" s="259"/>
-      <c r="D21" s="201"/>
-      <c r="E21" s="252"/>
-      <c r="F21" s="253"/>
+      <c r="A21" s="217"/>
+      <c r="B21" s="218"/>
+      <c r="C21" s="219"/>
+      <c r="D21" s="235"/>
+      <c r="E21" s="225"/>
+      <c r="F21" s="226"/>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="257"/>
-      <c r="B22" s="258"/>
-      <c r="C22" s="259"/>
+      <c r="A22" s="217"/>
+      <c r="B22" s="218"/>
+      <c r="C22" s="219"/>
     </row>
     <row r="23" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A23" s="257"/>
-      <c r="B23" s="258"/>
-      <c r="C23" s="259"/>
-      <c r="D23" s="199" t="s">
+      <c r="A23" s="217"/>
+      <c r="B23" s="218"/>
+      <c r="C23" s="219"/>
+      <c r="D23" s="233" t="s">
         <v>2</v>
       </c>
-      <c r="E23" s="250" t="s">
+      <c r="E23" s="223" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="251"/>
+      <c r="F23" s="224"/>
     </row>
     <row r="24" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A24" s="257"/>
-      <c r="B24" s="258"/>
-      <c r="C24" s="259"/>
-      <c r="D24" s="201"/>
-      <c r="E24" s="252"/>
-      <c r="F24" s="253"/>
+      <c r="A24" s="217"/>
+      <c r="B24" s="218"/>
+      <c r="C24" s="219"/>
+      <c r="D24" s="235"/>
+      <c r="E24" s="225"/>
+      <c r="F24" s="226"/>
     </row>
     <row r="25" spans="1:15" ht="28.5" customHeight="1">
-      <c r="A25" s="257"/>
-      <c r="B25" s="258"/>
-      <c r="C25" s="259"/>
+      <c r="A25" s="217"/>
+      <c r="B25" s="218"/>
+      <c r="C25" s="219"/>
     </row>
     <row r="26" spans="1:15" ht="36" customHeight="1">
-      <c r="A26" s="257"/>
-      <c r="B26" s="258"/>
-      <c r="C26" s="259"/>
-      <c r="D26" s="199" t="s">
+      <c r="A26" s="217"/>
+      <c r="B26" s="218"/>
+      <c r="C26" s="219"/>
+      <c r="D26" s="233" t="s">
         <v>2</v>
       </c>
-      <c r="E26" s="205" t="s">
+      <c r="E26" s="227" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="206"/>
-      <c r="G26" s="202" t="s">
+      <c r="F26" s="228"/>
+      <c r="G26" s="260" t="s">
         <v>2</v>
       </c>
-      <c r="H26" s="205" t="s">
+      <c r="H26" s="227" t="s">
         <v>13</v>
       </c>
-      <c r="I26" s="206"/>
-      <c r="J26" s="202" t="s">
+      <c r="I26" s="228"/>
+      <c r="J26" s="260" t="s">
         <v>2</v>
       </c>
-      <c r="K26" s="211" t="s">
+      <c r="K26" s="248" t="s">
         <v>14</v>
       </c>
-      <c r="L26" s="212"/>
+      <c r="L26" s="249"/>
       <c r="M26" s="174"/>
       <c r="N26" s="175"/>
       <c r="O26" s="139"/>
     </row>
     <row r="27" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A27" s="257"/>
-      <c r="B27" s="258"/>
-      <c r="C27" s="259"/>
-      <c r="D27" s="200"/>
-      <c r="E27" s="207"/>
-      <c r="F27" s="208"/>
-      <c r="G27" s="203"/>
-      <c r="H27" s="207"/>
-      <c r="I27" s="208"/>
-      <c r="J27" s="203"/>
-      <c r="K27" s="213"/>
-      <c r="L27" s="214"/>
+      <c r="A27" s="217"/>
+      <c r="B27" s="218"/>
+      <c r="C27" s="219"/>
+      <c r="D27" s="234"/>
+      <c r="E27" s="229"/>
+      <c r="F27" s="230"/>
+      <c r="G27" s="261"/>
+      <c r="H27" s="229"/>
+      <c r="I27" s="230"/>
+      <c r="J27" s="261"/>
+      <c r="K27" s="250"/>
+      <c r="L27" s="251"/>
       <c r="M27" s="176"/>
       <c r="N27" s="177"/>
       <c r="O27" s="139"/>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" s="257"/>
-      <c r="B28" s="258"/>
-      <c r="C28" s="259"/>
-      <c r="D28" s="200"/>
-      <c r="E28" s="207"/>
-      <c r="F28" s="208"/>
-      <c r="G28" s="203"/>
-      <c r="H28" s="207"/>
-      <c r="I28" s="208"/>
-      <c r="J28" s="204"/>
-      <c r="K28" s="215"/>
-      <c r="L28" s="216"/>
+      <c r="A28" s="217"/>
+      <c r="B28" s="218"/>
+      <c r="C28" s="219"/>
+      <c r="D28" s="234"/>
+      <c r="E28" s="229"/>
+      <c r="F28" s="230"/>
+      <c r="G28" s="261"/>
+      <c r="H28" s="229"/>
+      <c r="I28" s="230"/>
+      <c r="J28" s="262"/>
+      <c r="K28" s="252"/>
+      <c r="L28" s="253"/>
       <c r="M28" s="178"/>
       <c r="N28" s="179"/>
       <c r="O28" s="139"/>
     </row>
     <row r="29" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A29" s="257"/>
-      <c r="B29" s="258"/>
-      <c r="C29" s="259"/>
-      <c r="D29" s="200"/>
-      <c r="E29" s="207"/>
-      <c r="F29" s="208"/>
-      <c r="G29" s="203"/>
-      <c r="H29" s="207"/>
-      <c r="I29" s="208"/>
+      <c r="A29" s="217"/>
+      <c r="B29" s="218"/>
+      <c r="C29" s="219"/>
+      <c r="D29" s="234"/>
+      <c r="E29" s="229"/>
+      <c r="F29" s="230"/>
+      <c r="G29" s="261"/>
+      <c r="H29" s="229"/>
+      <c r="I29" s="230"/>
       <c r="K29" s="140"/>
       <c r="L29" s="140"/>
       <c r="M29" s="140"/>
@@ -5718,68 +5764,68 @@
       <c r="O29" s="332"/>
     </row>
     <row r="30" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A30" s="257"/>
-      <c r="B30" s="258"/>
-      <c r="C30" s="259"/>
-      <c r="D30" s="200"/>
-      <c r="E30" s="207"/>
-      <c r="F30" s="208"/>
-      <c r="G30" s="203"/>
-      <c r="H30" s="207"/>
-      <c r="I30" s="208"/>
-      <c r="J30" s="202" t="s">
+      <c r="A30" s="217"/>
+      <c r="B30" s="218"/>
+      <c r="C30" s="219"/>
+      <c r="D30" s="234"/>
+      <c r="E30" s="229"/>
+      <c r="F30" s="230"/>
+      <c r="G30" s="261"/>
+      <c r="H30" s="229"/>
+      <c r="I30" s="230"/>
+      <c r="J30" s="260" t="s">
         <v>2</v>
       </c>
-      <c r="K30" s="217" t="s">
+      <c r="K30" s="254" t="s">
         <v>15</v>
       </c>
-      <c r="L30" s="218"/>
+      <c r="L30" s="255"/>
       <c r="M30" s="180"/>
       <c r="N30" s="181"/>
       <c r="O30" s="139"/>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31" s="257"/>
-      <c r="B31" s="258"/>
-      <c r="C31" s="259"/>
-      <c r="D31" s="200"/>
-      <c r="E31" s="207"/>
-      <c r="F31" s="208"/>
-      <c r="G31" s="203"/>
-      <c r="H31" s="207"/>
-      <c r="I31" s="208"/>
-      <c r="J31" s="203"/>
-      <c r="K31" s="219"/>
-      <c r="L31" s="220"/>
+      <c r="A31" s="217"/>
+      <c r="B31" s="218"/>
+      <c r="C31" s="219"/>
+      <c r="D31" s="234"/>
+      <c r="E31" s="229"/>
+      <c r="F31" s="230"/>
+      <c r="G31" s="261"/>
+      <c r="H31" s="229"/>
+      <c r="I31" s="230"/>
+      <c r="J31" s="261"/>
+      <c r="K31" s="256"/>
+      <c r="L31" s="257"/>
       <c r="M31" s="182"/>
       <c r="N31" s="183"/>
       <c r="O31" s="139"/>
     </row>
     <row r="32" spans="1:15">
-      <c r="A32" s="260"/>
-      <c r="B32" s="261"/>
-      <c r="C32" s="262"/>
-      <c r="D32" s="201"/>
-      <c r="E32" s="209"/>
-      <c r="F32" s="210"/>
-      <c r="G32" s="204"/>
-      <c r="H32" s="209"/>
-      <c r="I32" s="210"/>
-      <c r="J32" s="204"/>
-      <c r="K32" s="221"/>
-      <c r="L32" s="222"/>
+      <c r="A32" s="220"/>
+      <c r="B32" s="221"/>
+      <c r="C32" s="222"/>
+      <c r="D32" s="235"/>
+      <c r="E32" s="231"/>
+      <c r="F32" s="232"/>
+      <c r="G32" s="262"/>
+      <c r="H32" s="231"/>
+      <c r="I32" s="232"/>
+      <c r="J32" s="262"/>
+      <c r="K32" s="258"/>
+      <c r="L32" s="259"/>
       <c r="M32" s="184"/>
       <c r="N32" s="185"/>
       <c r="O32" s="139"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="269" t="s">
+      <c r="A35" s="205" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="270"/>
-      <c r="C35" s="270"/>
-      <c r="D35" s="270"/>
-      <c r="E35" s="271"/>
+      <c r="B35" s="206"/>
+      <c r="C35" s="206"/>
+      <c r="D35" s="206"/>
+      <c r="E35" s="207"/>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="141"/>
@@ -5921,11 +5967,30 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="N2:O4"/>
+    <mergeCell ref="M2:M4"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="D9:D15"/>
+    <mergeCell ref="D26:D32"/>
+    <mergeCell ref="G26:G32"/>
+    <mergeCell ref="J26:J28"/>
+    <mergeCell ref="J30:J32"/>
+    <mergeCell ref="G9:G15"/>
+    <mergeCell ref="J9:J15"/>
+    <mergeCell ref="H26:I32"/>
+    <mergeCell ref="K26:L28"/>
+    <mergeCell ref="K30:L32"/>
+    <mergeCell ref="H9:I15"/>
+    <mergeCell ref="H6:I7"/>
+    <mergeCell ref="K9:L15"/>
+    <mergeCell ref="K2:L4"/>
+    <mergeCell ref="E9:F15"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="E20:F21"/>
+    <mergeCell ref="N9:O11"/>
+    <mergeCell ref="N13:O15"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="M13:M15"/>
     <mergeCell ref="Q2:R4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="P2:P4"/>
@@ -5942,30 +6007,11 @@
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="E2:F4"/>
     <mergeCell ref="E6:F7"/>
-    <mergeCell ref="E9:F15"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="E20:F21"/>
-    <mergeCell ref="N9:O11"/>
-    <mergeCell ref="N13:O15"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="M13:M15"/>
-    <mergeCell ref="M2:M4"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="D9:D15"/>
-    <mergeCell ref="D26:D32"/>
-    <mergeCell ref="G26:G32"/>
-    <mergeCell ref="J26:J28"/>
-    <mergeCell ref="J30:J32"/>
-    <mergeCell ref="G9:G15"/>
-    <mergeCell ref="J9:J15"/>
-    <mergeCell ref="H26:I32"/>
-    <mergeCell ref="K26:L28"/>
-    <mergeCell ref="K30:L32"/>
-    <mergeCell ref="H9:I15"/>
-    <mergeCell ref="H6:I7"/>
-    <mergeCell ref="K9:L15"/>
-    <mergeCell ref="K2:L4"/>
-    <mergeCell ref="N2:O4"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15219,15 +15265,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
@@ -15237,14 +15274,23 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
 </file>